--- a/artfynd/A 26678-2024 artfynd.xlsx
+++ b/artfynd/A 26678-2024 artfynd.xlsx
@@ -1788,10 +1788,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118312812</v>
+        <v>118301120</v>
       </c>
       <c r="B11" t="n">
-        <v>101185</v>
+        <v>97846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1800,35 +1800,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221317</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kramnästorp 200m V, Srm</t>
+          <t>Kramnästorp 250m V, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1880,9 +1888,9 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Åkermark</t>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1900,10 +1908,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118301120</v>
+        <v>118312812</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>101185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1912,43 +1920,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kramnästorp 250m V, Srm</t>
+          <t>Kramnästorp 200m V, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -2000,9 +2000,9 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Åkermark</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 26678-2024 artfynd.xlsx
+++ b/artfynd/A 26678-2024 artfynd.xlsx
@@ -1791,7 +1791,7 @@
         <v>118301120</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>118312812</v>
       </c>
       <c r="B12" t="n">
-        <v>101185</v>
+        <v>101192</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
